--- a/data/trans_orig/P33A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>340587</t>
+          <t>340282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>371857</t>
+          <t>374743</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>220765</t>
+          <t>222097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>251841</t>
+          <t>253871</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>572658</t>
+          <t>571689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>618715</t>
+          <t>616688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63470</t>
+          <t>60584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94740</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>58638</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91744</t>
+          <t>90412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129121</t>
+          <t>131148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175178</t>
+          <t>176147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>326861</t>
+          <t>325400</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>360777</t>
+          <t>359096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232515</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>265017</t>
+          <t>267125</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>572341</t>
+          <t>572080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>618172</t>
+          <t>618033</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,09%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55102</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89018</t>
+          <t>90479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>71948</t>
+          <t>69840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104450</t>
+          <t>103398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134672</t>
+          <t>134811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180503</t>
+          <t>180764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,01%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>532629</t>
+          <t>533619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>566771</t>
+          <t>566193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162963</t>
+          <t>165154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192498</t>
+          <t>195065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>706448</t>
+          <t>707422</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>750939</t>
+          <t>755171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93684</t>
+          <t>92694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64290</t>
+          <t>61723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93825</t>
+          <t>91634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132162</t>
+          <t>127930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176653</t>
+          <t>175679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>950212</t>
+          <t>951344</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1000455</t>
+          <t>1000263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>519108</t>
+          <t>518402</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569735</t>
+          <t>569305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1482959</t>
+          <t>1481937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1556824</t>
+          <t>1558446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148513</t>
+          <t>148705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198756</t>
+          <t>197624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188027</t>
+          <t>188457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>238654</t>
+          <t>239360</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349906</t>
+          <t>348284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>423771</t>
+          <t>424793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>412400</t>
+          <t>413496</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>445727</t>
+          <t>444774</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>508652</t>
+          <t>507717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>559806</t>
+          <t>559906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>930968</t>
+          <t>936039</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>994531</t>
+          <t>995314</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,56%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>62530</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94904</t>
+          <t>93808</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199799</t>
+          <t>199699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>250953</t>
+          <t>251888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272378</t>
+          <t>271595</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335941</t>
+          <t>330870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210321</t>
+          <t>211730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>232418</t>
+          <t>233651</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>80,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>806893</t>
+          <t>806770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>863368</t>
+          <t>865585</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1026931</t>
+          <t>1029581</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1089261</t>
+          <t>1090600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,96%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>30291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53621</t>
+          <t>52212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>236594</t>
+          <t>234377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293069</t>
+          <t>293192</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274643</t>
+          <t>273304</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>336973</t>
+          <t>334323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2839427</t>
+          <t>2840581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2927353</t>
+          <t>2925455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2531495</t>
+          <t>2531620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2635147</t>
+          <t>2636979</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5402598</t>
+          <t>5396607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5539652</t>
+          <t>5531989</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>470380</t>
+          <t>472278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>558306</t>
+          <t>557152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>888443</t>
+          <t>886611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>992095</t>
+          <t>991970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381671</t>
+          <t>1389334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1518725</t>
+          <t>1524716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2016 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334778</t>
+          <t>336467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367879</t>
+          <t>370227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231435</t>
+          <t>231209</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265491</t>
+          <t>264346</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>577292</t>
+          <t>575975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>626423</t>
+          <t>624762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54780</t>
+          <t>52432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87881</t>
+          <t>86192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75892</t>
+          <t>77037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>109948</t>
+          <t>110174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>137619</t>
+          <t>139280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186750</t>
+          <t>188067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>280005</t>
+          <t>278232</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310575</t>
+          <t>310721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>261075</t>
+          <t>260884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>295816</t>
+          <t>294689</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>551036</t>
+          <t>553065</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596627</t>
+          <t>597307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60184</t>
+          <t>60038</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90754</t>
+          <t>92527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74010</t>
+          <t>75137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108751</t>
+          <t>108942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143958</t>
+          <t>143278</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189549</t>
+          <t>187520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>421674</t>
+          <t>422207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>454934</t>
+          <t>456228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99566</t>
+          <t>98504</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123565</t>
+          <t>123109</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>529676</t>
+          <t>531370</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>572595</t>
+          <t>573518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,98%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63950</t>
+          <t>62656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97210</t>
+          <t>96677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40491</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>65552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110344</t>
+          <t>109421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>153263</t>
+          <t>151569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>937362</t>
+          <t>938397</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>985920</t>
+          <t>986645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>553798</t>
+          <t>551718</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>608438</t>
+          <t>604257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1503964</t>
+          <t>1505332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1578646</t>
+          <t>1579702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,8%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150195</t>
+          <t>149470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198753</t>
+          <t>197718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>210632</t>
+          <t>214813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265272</t>
+          <t>267352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>376539</t>
+          <t>375483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>451221</t>
+          <t>449853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>493919</t>
+          <t>493343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>531827</t>
+          <t>532146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>481454</t>
+          <t>482027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530550</t>
+          <t>532024</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>984988</t>
+          <t>988983</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1050551</t>
+          <t>1050279</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83721</t>
+          <t>83402</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121629</t>
+          <t>122205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200221</t>
+          <t>198747</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>249317</t>
+          <t>248744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295769</t>
+          <t>296041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361332</t>
+          <t>357337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>238430</t>
+          <t>237573</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261568</t>
+          <t>260770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>810677</t>
+          <t>813732</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>867757</t>
+          <t>868797</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1059308</t>
+          <t>1058729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1121005</t>
+          <t>1117710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23603</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>47598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193355</t>
+          <t>192315</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>250435</t>
+          <t>247380</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>225278</t>
+          <t>228573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>286975</t>
+          <t>287554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2775573</t>
+          <t>2771537</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2861948</t>
+          <t>2855825</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2512134</t>
+          <t>2513693</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2621847</t>
+          <t>2618512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5315418</t>
+          <t>5314068</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5454618</t>
+          <t>5455222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>487188</t>
+          <t>493311</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>573563</t>
+          <t>577599</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>864372</t>
+          <t>867707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>974085</t>
+          <t>972526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380737</t>
+          <t>1380133</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1519937</t>
+          <t>1521287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023</t>
+          <t>Población que las horas que duerme le permiten descansar lo suficiente en 2023 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>400645</t>
+          <t>400962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>434938</t>
+          <t>436459</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>338404</t>
+          <t>339237</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>366463</t>
+          <t>368108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>745795</t>
+          <t>749159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>792985</t>
+          <t>796403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70274</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104567</t>
+          <t>104250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>76321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106025</t>
+          <t>105192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>156656</t>
+          <t>153238</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203846</t>
+          <t>200482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>357126</t>
+          <t>356304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>387134</t>
+          <t>388021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273571</t>
+          <t>275226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302679</t>
+          <t>302990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>640926</t>
+          <t>642716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>683538</t>
+          <t>684540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,75%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>60757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91652</t>
+          <t>92474</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75811</t>
+          <t>75500</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>103264</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143730</t>
+          <t>142728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186342</t>
+          <t>184552</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>520223</t>
+          <t>518741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>634097</t>
+          <t>634431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106038</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>124646</t>
+          <t>125275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>630127</t>
+          <t>629848</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>774757</t>
+          <t>770954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,42%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33151</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147025</t>
+          <t>148507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42265</t>
+          <t>41636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60873</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59401</t>
+          <t>63204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204031</t>
+          <t>204310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,49%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>785370</t>
+          <t>786138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>844355</t>
+          <t>846512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>713879</t>
+          <t>716259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>871157</t>
+          <t>875027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1534452</t>
+          <t>1533436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1712063</t>
+          <t>1707078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>185653</t>
+          <t>183496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244638</t>
+          <t>243870</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99540</t>
+          <t>95670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256818</t>
+          <t>254438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288641</t>
+          <t>293626</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>466252</t>
+          <t>467268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>370273</t>
+          <t>368839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402744</t>
+          <t>402462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>578828</t>
+          <t>578382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667473</t>
+          <t>667786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>966190</t>
+          <t>964484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1056665</t>
+          <t>1059045</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,93%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70069</t>
+          <t>70351</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>103974</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168344</t>
+          <t>168031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256989</t>
+          <t>257435</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251964</t>
+          <t>249584</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342439</t>
+          <t>344145</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>217997</t>
+          <t>216886</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233072</t>
+          <t>232736</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>540498</t>
+          <t>539686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>581987</t>
+          <t>580824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>767971</t>
+          <t>764462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>812566</t>
+          <t>811067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,93%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>171297</t>
+          <t>172460</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>212786</t>
+          <t>213598</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>177403</t>
+          <t>178902</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>221998</t>
+          <t>225507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,78%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2741317</t>
+          <t>2739755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2917574</t>
+          <t>2929566</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2633738</t>
+          <t>2627770</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2867127</t>
+          <t>2868720</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5404560</t>
+          <t>5410297</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5702827</t>
+          <t>5705004</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>443169</t>
+          <t>431177</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>619426</t>
+          <t>620988</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682500</t>
+          <t>680907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>915889</t>
+          <t>921857</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1207542</t>
+          <t>1205365</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1505809</t>
+          <t>1500072</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33A-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>340282</t>
+          <t>340869</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>374743</t>
+          <t>373191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222097</t>
+          <t>221834</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>253871</t>
+          <t>253206</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>571689</t>
+          <t>574253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>616688</t>
+          <t>619080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60584</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95045</t>
+          <t>94458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58638</t>
+          <t>59303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90412</t>
+          <t>90675</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>131148</t>
+          <t>128756</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176147</t>
+          <t>173583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325400</t>
+          <t>325685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359096</t>
+          <t>358893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>233567</t>
+          <t>232851</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267125</t>
+          <t>266353</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>572080</t>
+          <t>571980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>618033</t>
+          <t>617850</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56783</t>
+          <t>56986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90479</t>
+          <t>90194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69840</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103398</t>
+          <t>104114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134811</t>
+          <t>134994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180764</t>
+          <t>180864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>533619</t>
+          <t>533062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>566193</t>
+          <t>566062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165154</t>
+          <t>164727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195065</t>
+          <t>196469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>707422</t>
+          <t>705657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>755171</t>
+          <t>752829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,25%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60120</t>
+          <t>60251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92694</t>
+          <t>93251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>60319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91634</t>
+          <t>92061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>127930</t>
+          <t>130272</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175679</t>
+          <t>177444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>951344</t>
+          <t>948373</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1000263</t>
+          <t>1000547</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>518402</t>
+          <t>520295</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>569305</t>
+          <t>570997</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1481937</t>
+          <t>1483701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1558446</t>
+          <t>1558801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,75%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148705</t>
+          <t>148421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197624</t>
+          <t>200595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188457</t>
+          <t>186765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>239360</t>
+          <t>237467</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348284</t>
+          <t>347929</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>424793</t>
+          <t>423029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>413496</t>
+          <t>413714</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>444774</t>
+          <t>446143</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>507717</t>
+          <t>507840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>559906</t>
+          <t>559828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>936039</t>
+          <t>931335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>995314</t>
+          <t>996233</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62530</t>
+          <t>61161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93808</t>
+          <t>93590</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>199699</t>
+          <t>199777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251888</t>
+          <t>251765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271595</t>
+          <t>270676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>330870</t>
+          <t>335574</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>211730</t>
+          <t>208898</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>233651</t>
+          <t>232478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>806770</t>
+          <t>803341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>865585</t>
+          <t>863077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1029581</t>
+          <t>1022465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1090600</t>
+          <t>1085798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52212</t>
+          <t>55044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234377</t>
+          <t>236885</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>293192</t>
+          <t>296621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273304</t>
+          <t>278106</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>334323</t>
+          <t>341439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2840581</t>
+          <t>2836764</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2925455</t>
+          <t>2927938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2531620</t>
+          <t>2528255</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2636979</t>
+          <t>2637151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5396607</t>
+          <t>5398288</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5531989</t>
+          <t>5536000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472278</t>
+          <t>469795</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>557152</t>
+          <t>560969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>886611</t>
+          <t>886439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>991970</t>
+          <t>995335</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1389334</t>
+          <t>1385323</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1524716</t>
+          <t>1523035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>336467</t>
+          <t>335902</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>370227</t>
+          <t>367561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231209</t>
+          <t>231671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264346</t>
+          <t>266248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>575975</t>
+          <t>576809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>624762</t>
+          <t>623842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,65%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52432</t>
+          <t>55098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>86757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77037</t>
+          <t>75135</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110174</t>
+          <t>109712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139280</t>
+          <t>140200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188067</t>
+          <t>187233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>278232</t>
+          <t>279606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>310721</t>
+          <t>311014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260884</t>
+          <t>260236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294689</t>
+          <t>295054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>553065</t>
+          <t>552826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>597307</t>
+          <t>597551</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60038</t>
+          <t>59745</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92527</t>
+          <t>91153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75137</t>
+          <t>74772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>108942</t>
+          <t>109590</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143278</t>
+          <t>143034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187520</t>
+          <t>187759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>422207</t>
+          <t>422382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>456228</t>
+          <t>455213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98504</t>
+          <t>99075</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123109</t>
+          <t>123358</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>531370</t>
+          <t>531308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573518</t>
+          <t>572634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>96502</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40947</t>
+          <t>40698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65552</t>
+          <t>64981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109421</t>
+          <t>110305</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151569</t>
+          <t>151631</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>938397</t>
+          <t>937193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>986645</t>
+          <t>988344</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>551718</t>
+          <t>549917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>604257</t>
+          <t>604610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1505332</t>
+          <t>1507900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1579702</t>
+          <t>1583004</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149470</t>
+          <t>147771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197718</t>
+          <t>198922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>214813</t>
+          <t>214460</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>267352</t>
+          <t>269153</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>375483</t>
+          <t>372181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>449853</t>
+          <t>447285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>493343</t>
+          <t>491033</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>532146</t>
+          <t>531488</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>482027</t>
+          <t>479743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>532024</t>
+          <t>529752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>988983</t>
+          <t>988695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1050279</t>
+          <t>1051951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,14%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83402</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>124515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198747</t>
+          <t>201019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>248744</t>
+          <t>251028</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>296041</t>
+          <t>294369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357337</t>
+          <t>357625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237573</t>
+          <t>239798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260770</t>
+          <t>261435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>813732</t>
+          <t>813473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>868797</t>
+          <t>867264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1058729</t>
+          <t>1062415</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1117710</t>
+          <t>1120521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47598</t>
+          <t>45373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192315</t>
+          <t>193848</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247380</t>
+          <t>247639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228573</t>
+          <t>225762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>287554</t>
+          <t>283868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2771537</t>
+          <t>2771000</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2855825</t>
+          <t>2855854</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2513693</t>
+          <t>2511373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2618512</t>
+          <t>2625194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5314068</t>
+          <t>5311843</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5455222</t>
+          <t>5452586</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,77%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>493311</t>
+          <t>493282</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577599</t>
+          <t>578136</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>867707</t>
+          <t>861025</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>972526</t>
+          <t>974846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1380133</t>
+          <t>1382769</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1521287</t>
+          <t>1523512</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>419754</t>
+          <t>458900</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>400962</t>
+          <t>440674</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>436459</t>
+          <t>477233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>353032</t>
+          <t>382885</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>339237</t>
+          <t>368065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>368108</t>
+          <t>398107</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>772786</t>
+          <t>841785</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>749159</t>
+          <t>813139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>796403</t>
+          <t>865571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85458</t>
+          <t>91718</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68753</t>
+          <t>73385</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104250</t>
+          <t>109944</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91397</t>
+          <t>102344</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76321</t>
+          <t>87122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>105192</t>
+          <t>117164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>176855</t>
+          <t>194062</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153238</t>
+          <t>170276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200482</t>
+          <t>222708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,5%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>444429</t>
+          <t>485229</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>444429</t>
+          <t>485229</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>444429</t>
+          <t>485229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>949641</t>
+          <t>1035847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>949641</t>
+          <t>1035847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>949641</t>
+          <t>1035847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>373396</t>
+          <t>399871</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>356304</t>
+          <t>381167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>388021</t>
+          <t>414485</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289950</t>
+          <t>319906</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>275226</t>
+          <t>303616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>302990</t>
+          <t>334089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>663347</t>
+          <t>719776</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642716</t>
+          <t>695661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>684540</t>
+          <t>743140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>79630</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60757</t>
+          <t>65016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92474</t>
+          <t>98334</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>99132</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75500</t>
+          <t>84949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103264</t>
+          <t>115422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>163921</t>
+          <t>178763</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142728</t>
+          <t>155399</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184552</t>
+          <t>202878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448778</t>
+          <t>479501</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448778</t>
+          <t>479501</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448778</t>
+          <t>479501</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>378490</t>
+          <t>419038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>378490</t>
+          <t>419038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>378490</t>
+          <t>419038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>827268</t>
+          <t>898539</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>827268</t>
+          <t>898539</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>827268</t>
+          <t>898539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>579412</t>
+          <t>377897</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>518741</t>
+          <t>360026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>634431</t>
+          <t>395029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>115407</t>
+          <t>129466</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106104</t>
+          <t>119542</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125275</t>
+          <t>139793</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>694818</t>
+          <t>507363</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>629848</t>
+          <t>488058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>770954</t>
+          <t>527802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>80,2%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87836</t>
+          <t>92736</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>75604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148507</t>
+          <t>110607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51504</t>
+          <t>58031</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>47704</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60807</t>
+          <t>67955</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>139340</t>
+          <t>150767</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63204</t>
+          <t>130328</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204310</t>
+          <t>170072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667248</t>
+          <t>470633</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834158</t>
+          <t>658130</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,102 +7026,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>817721</t>
+          <t>905985</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>786138</t>
+          <t>876844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>846512</t>
+          <t>932473</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>630139</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>606199</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>651953</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>73,85%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>71,04%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>76,4%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1536123</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1498121</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1571789</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>77,58%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>75,67%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>79,39%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,32%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>82,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>906</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>775724</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>716259</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>875027</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>79,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>73,79%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1792</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1593444</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1533436</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1707078</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>79,64%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>76,64%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -7139,102 +7139,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>212287</t>
+          <t>220638</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183496</t>
+          <t>194150</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243870</t>
+          <t>249779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>223170</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201356</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>247110</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>26,15%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>23,6%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>28,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>542</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>443808</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>408142</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>481810</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>22,42%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>20,61%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>17,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,68%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>194973</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95670</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>254438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>407260</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>293626</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>467268</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1030008</t>
+          <t>1126623</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1030008</t>
+          <t>1126623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1030008</t>
+          <t>1126623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>970697</t>
+          <t>853309</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>970697</t>
+          <t>853309</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>970697</t>
+          <t>853309</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2000704</t>
+          <t>1979931</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2000704</t>
+          <t>1979931</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2000704</t>
+          <t>1979931</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>387690</t>
+          <t>472408</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>368839</t>
+          <t>454259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>402462</t>
+          <t>490881</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>612209</t>
+          <t>579665</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>578382</t>
+          <t>558035</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667786</t>
+          <t>601457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>999898</t>
+          <t>1052073</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>964484</t>
+          <t>1023737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1059045</t>
+          <t>1081211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>77,66%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>93084</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70351</t>
+          <t>74611</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>111233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>223608</t>
+          <t>247127</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>168031</t>
+          <t>225335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>257435</t>
+          <t>268757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>308731</t>
+          <t>340211</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249584</t>
+          <t>311073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344145</t>
+          <t>368547</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,47%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>472813</t>
+          <t>565492</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>472813</t>
+          <t>565492</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>472813</t>
+          <t>565492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>835817</t>
+          <t>826792</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>835817</t>
+          <t>826792</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>835817</t>
+          <t>826792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1308629</t>
+          <t>1392284</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1308629</t>
+          <t>1392284</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1308629</t>
+          <t>1392284</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>227654</t>
+          <t>222318</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>216886</t>
+          <t>213041</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>232736</t>
+          <t>228619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>561545</t>
+          <t>620644</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>539686</t>
+          <t>598011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>580824</t>
+          <t>644143</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>789200</t>
+          <t>842964</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>764462</t>
+          <t>818374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>811067</t>
+          <t>864846</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>191739</t>
+          <t>215253</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172460</t>
+          <t>191754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>213598</t>
+          <t>237886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>200769</t>
+          <t>226771</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>178902</t>
+          <t>204889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>225507</t>
+          <t>251361</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -7938,17 +7938,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>236685</t>
+          <t>233837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>236685</t>
+          <t>233837</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>236685</t>
+          <t>233837</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>753284</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>753284</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>753284</t>
+          <t>835897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>989969</t>
+          <t>1069735</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>989969</t>
+          <t>1069735</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>989969</t>
+          <t>1069735</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2805626</t>
+          <t>2837379</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2739755</t>
+          <t>2793660</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2929566</t>
+          <t>2884246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2707867</t>
+          <t>2662706</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2627770</t>
+          <t>2611508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2868720</t>
+          <t>2702924</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>5513493</t>
+          <t>5500085</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5410297</t>
+          <t>5434302</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5705004</t>
+          <t>5566987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>555117</t>
+          <t>589325</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>431177</t>
+          <t>542458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>620988</t>
+          <t>633044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841760</t>
+          <t>945056</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>680907</t>
+          <t>904838</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>921857</t>
+          <t>996254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1396876</t>
+          <t>1534381</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1205365</t>
+          <t>1467479</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1500072</t>
+          <t>1600164</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3360743</t>
+          <t>3426704</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3360743</t>
+          <t>3426704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3360743</t>
+          <t>3426704</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3549627</t>
+          <t>3607762</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3549627</t>
+          <t>3607762</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3549627</t>
+          <t>3607762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6910369</t>
+          <t>7034466</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6910369</t>
+          <t>7034466</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6910369</t>
+          <t>7034466</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
